--- a/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-4,08; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-1,97; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,0</t>
+          <t>-1,82; 0,0</t>
         </is>
       </c>
     </row>
@@ -797,17 +797,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,98</t>
+          <t>-0,17; 0,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,59</t>
+          <t>-0,29; 0,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,58</t>
+          <t>-0,09; 0,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,0</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,69</t>
+          <t>-1,7; 0,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,22; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 0,36</t>
+          <t>-0,8; 0,36</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,17 +1109,17 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,37</t>
+          <t>-0,58; 0,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,27</t>
+          <t>-0,58; 0,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,27</t>
+          <t>-0,22; 0,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
@@ -641,22 +641,22 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,0</t>
+          <t>-3,46; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-4,01; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,17 +797,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,86</t>
+          <t>-0,17; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,45</t>
+          <t>-0,29; 0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 0,51</t>
+          <t>-0,08; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,22 +953,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,69</t>
+          <t>-1,53; 0,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,0</t>
+          <t>-0,94; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,36</t>
+          <t>-0,64; 0,36</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,37</t>
+          <t>-0,47; 0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,24</t>
+          <t>-0,21; 0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,13</t>
+          <t>-0,3; 0,1</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,23; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,17 +749,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>-0,29; 0,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,29; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,87</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,57</t>
+          <t>-0,08; 0,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>182,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>182,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,43</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,61; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,29; 0,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,0</t>
+          <t>-1,19; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,36</t>
+          <t>-0,61; 0,36</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-19,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-19,09%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>-0,49; 0,37</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-0,57; 0,27</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,34</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,47; 0,45</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 0,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,25</t>
+          <t>-0,2; 0,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,1</t>
+          <t>-0,3; 0,13</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-4,93%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-36,27%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-4,93%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-36,27%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,255 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.8064934839223634</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.8064934839223634</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-0.3941188925092189</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3941188925092189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,03; 0,0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-2,37; 0,0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-2,23; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-4.030376308962637</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-4.027618538583448</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="n">
+        <v>-2.36909894554567</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-2.232524910753158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-0,0</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 0,98</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,29; 0,59</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,54</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-0,08; 0,58</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,24; 0,15</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>182,34%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>241,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-4,74%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2677433790363177</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>6.724080282658612e-05</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1067272938726735</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.1892058177672899</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.003716221818558134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.2924710795207546</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.2942990257846082</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="n">
+        <v>-0.08303627042289835</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.2358369493304592</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.977760260399098</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.5851257909260842</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.5357047903062189</v>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
+      <c r="G12" s="5" t="n">
+        <v>0.5761339840217186</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.1502352682587947</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,29; 0,69</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-1,19; 0,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 0,36</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>1.823414924845507</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.0004579305896335912</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="n">
+        <v>2.412574819241666</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.04738576904224464</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-19,09%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-11,53%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +856,253 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-0.4256821102391004</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.08128116356022141</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.2026360666034461</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.02336374220658095</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 0,37</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 0,27</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,34</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,2; 0,27</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,3; 0,13</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.607271813568509</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.286946316366319</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="n">
+        <v>-1.186846161370051</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.6117086345444912</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>-4,93%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-36,27%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17,27%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-36,34%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6903330983650959</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr"/>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.362169260477071</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.1909433391846484</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.1152990314024562</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-0.01416491771212701</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.1041764651112413</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.06789264307066271</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.02553355776586384</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.05372417293445822</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.4931657867347551</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.5724614080116635</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="n">
+        <v>-0.202519819585276</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.2988537563875959</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.3719237074621336</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.2729561013207618</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3421863840013424</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="n">
+        <v>0.2694005334208877</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.1336889291373846</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-0.04931006876003693</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.3626529120896339</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="n">
+        <v>0.1727299220262368</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.3634343590887786</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr"/>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr"/>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1110,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
